--- a/assets/libreoffice_calc_njc/696790a0-8164-4b34-b5b6-223a2495f530/QtrComprehensive_L3_05.xlsx
+++ b/assets/libreoffice_calc_njc/696790a0-8164-4b34-b5b6-223a2495f530/QtrComprehensive_L3_05.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t xml:space="preserve">Department</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1</t>
   </si>
   <si>
     <t xml:space="preserve">Q1-Q2 Growth %</t>
@@ -178,11 +175,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -223,7 +220,7 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -265,269 +262,273 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>220000</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>250000</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>280000</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <f aca="false">B2+D2+F2+H2</f>
         <v>950000</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <f aca="false">C2+E2+G2+I2</f>
         <v>460000</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <f aca="false">J2-K2</f>
         <v>490000</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">ROUND(L2/J2*100,1)</f>
         <v>51.6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>150000</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>165000</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>125000</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>180000</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>140000</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <f aca="false">B3+D3+F3+H3</f>
         <v>695000</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <f aca="false">C3+E3+G3+I3</f>
         <v>515000</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <f aca="false">J3-K3</f>
         <v>180000</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <f aca="false">ROUND(L3/J3*100,1)</f>
         <v>25.9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>80000</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <f aca="false">B4+D4+F4+H4</f>
         <v>375000</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <f aca="false">C4+E4+G4+I4</f>
         <v>270000</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <f aca="false">J4-K4</f>
         <v>105000</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <f aca="false">ROUND(L4/J4*100,1)</f>
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>85000</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <f aca="false">B5+D5+F5+H5</f>
         <v>460000</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <f aca="false">C5+E5+G5+I5</f>
         <v>370000</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <f aca="false">J5-K5</f>
         <v>90000</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <f aca="false">ROUND(L5/J5*100,1)</f>
         <v>19.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>32000</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>26000</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>28000</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>38000</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <f aca="false">B6+D6+F6+H6</f>
         <v>135000</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <f aca="false">C6+E6+G6+I6</f>
         <v>109000</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <f aca="false">J6-K6</f>
         <v>26000</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <f aca="false">ROUND(L6/J6*100,1)</f>
         <v>19.3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>560000</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>390000</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>617000</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>416000</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>680000</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>443000</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>758000</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>475000</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
+        <f aca="false">SUM(J2:J6)</f>
         <v>2615000</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
+        <f aca="false">SUM(K2:K6)</f>
         <v>1724000</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
+        <f aca="false">J7-K7</f>
         <v>891000</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>19</v>
+      <c r="M7" s="1" t="n">
+        <f aca="false">ROUND(L7/J7*100,1)</f>
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>
@@ -547,105 +548,105 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!C2-'Q1-Q4'!B2)/'Q1-Q4'!B2*100,1)</f>
-        <v>-50</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D2-'Q1-Q4'!C2)/'Q1-Q4'!C2*100,1)</f>
-        <v>120</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D2-'Q1-Q4'!E2)/'Q1-Q4'!E2*100,1)</f>
-        <v>100</v>
+      <c r="B2" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D2-'Q1-Q4'!B2)/'Q1-Q4'!B2*100,1)</f>
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!F2-'Q1-Q4'!D2)/'Q1-Q4'!D2*100,1)</f>
+        <v>13.6</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!H2-'Q1-Q4'!F2)/'Q1-Q4'!F2*100,1)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!C3-'Q1-Q4'!B3)/'Q1-Q4'!B3*100,1)</f>
-        <v>-20</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D3-'Q1-Q4'!C3)/'Q1-Q4'!C3*100,1)</f>
-        <v>37.5</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D3-'Q1-Q4'!E3)/'Q1-Q4'!E3*100,1)</f>
-        <v>32</v>
+      <c r="B3" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D3-'Q1-Q4'!B3)/'Q1-Q4'!B3*100,1)</f>
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!F3-'Q1-Q4'!D3)/'Q1-Q4'!D3*100,1)</f>
+        <v>9.1</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!H3-'Q1-Q4'!F3)/'Q1-Q4'!F3*100,1)</f>
+        <v>11.1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!C4-'Q1-Q4'!B4)/'Q1-Q4'!B4*100,1)</f>
-        <v>-25</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D4-'Q1-Q4'!C4)/'Q1-Q4'!C4*100,1)</f>
-        <v>50</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D4-'Q1-Q4'!E4)/'Q1-Q4'!E4*100,1)</f>
-        <v>38.5</v>
+      <c r="B4" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D4-'Q1-Q4'!B4)/'Q1-Q4'!B4*100,1)</f>
+        <v>12.5</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!F4-'Q1-Q4'!D4)/'Q1-Q4'!D4*100,1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!H4-'Q1-Q4'!F4)/'Q1-Q4'!F4*100,1)</f>
+        <v>15.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!C5-'Q1-Q4'!B5)/'Q1-Q4'!B5*100,1)</f>
-        <v>-15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D5-'Q1-Q4'!C5)/'Q1-Q4'!C5*100,1)</f>
-        <v>29.4</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D5-'Q1-Q4'!E5)/'Q1-Q4'!E5*100,1)</f>
-        <v>22.2</v>
+      <c r="B5" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D5-'Q1-Q4'!B5)/'Q1-Q4'!B5*100,1)</f>
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!F5-'Q1-Q4'!D5)/'Q1-Q4'!D5*100,1)</f>
+        <v>9.1</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!H5-'Q1-Q4'!F5)/'Q1-Q4'!F5*100,1)</f>
+        <v>8.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!C6-'Q1-Q4'!B6)/'Q1-Q4'!B6*100,1)</f>
-        <v>-16.7</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D6-'Q1-Q4'!C6)/'Q1-Q4'!C6*100,1)</f>
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D6-'Q1-Q4'!E6)/'Q1-Q4'!E6*100,1)</f>
-        <v>23.1</v>
+      <c r="B6" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D6-'Q1-Q4'!B6)/'Q1-Q4'!B6*100,1)</f>
+        <v>6.7</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!F6-'Q1-Q4'!D6)/'Q1-Q4'!D6*100,1)</f>
+        <v>9.4</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!H6-'Q1-Q4'!F6)/'Q1-Q4'!F6*100,1)</f>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/assets/libreoffice_calc_njc/696790a0-8164-4b34-b5b6-223a2495f530/QtrComprehensive_L3_05.xlsx
+++ b/assets/libreoffice_calc_njc/696790a0-8164-4b34-b5b6-223a2495f530/QtrComprehensive_L3_05.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t xml:space="preserve">Department</t>
   </si>
@@ -93,8 +93,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -170,8 +171,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -179,7 +184,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -217,7 +230,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -262,275 +275,285 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>200000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>110000</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>250000</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>120000</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>280000</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="2" t="n">
         <v>130000</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="3" t="n">
         <f aca="false">B2+D2+F2+H2</f>
         <v>950000</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="3" t="n">
         <f aca="false">C2+E2+G2+I2</f>
         <v>460000</v>
       </c>
-      <c r="L2" s="1" t="n">
-        <f aca="false">J2-K2</f>
+      <c r="L2" s="3" t="n">
+        <f aca="false">SUM(J2-K2)</f>
         <v>490000</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <f aca="false">ROUND(L2/J2*100,1)</f>
         <v>51.6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>150000</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>120000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>165000</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>125000</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>180000</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>130000</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>200000</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="2" t="n">
         <v>140000</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <f aca="false">B3+D3+F3+H3</f>
         <v>695000</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <f aca="false">C3+E3+G3+I3</f>
         <v>515000</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="2" t="n">
         <f aca="false">J3-K3</f>
         <v>180000</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <f aca="false">ROUND(L3/J3*100,1)</f>
         <v>25.9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>60000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>65000</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>95000</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>70000</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>110000</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="2" t="n">
         <v>75000</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <f aca="false">B4+D4+F4+H4</f>
         <v>375000</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <f aca="false">C4+E4+G4+I4</f>
         <v>270000</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <f aca="false">J4-K4</f>
         <v>105000</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <f aca="false">ROUND(L4/J4*100,1)</f>
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>85000</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>110000</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>120000</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>95000</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>130000</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <f aca="false">B5+D5+F5+H5</f>
         <v>460000</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <f aca="false">C5+E5+G5+I5</f>
         <v>370000</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <f aca="false">J5-K5</f>
         <v>90000</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <f aca="false">ROUND(L5/J5*100,1)</f>
         <v>19.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>25000</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>26000</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>35000</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>28000</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>38000</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="J6" s="1" t="n">
-        <f aca="false">B6+D6+F6+H6</f>
-        <v>135000</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <f aca="false">C6+E6+G6+I6</f>
-        <v>109000</v>
-      </c>
-      <c r="L6" s="1" t="n">
+      <c r="J6" s="2" t="n">
+        <f aca="false">SUM(B6:H6)</f>
+        <v>214000</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <f aca="false">SUM(C6:I6)</f>
+        <v>214000</v>
+      </c>
+      <c r="L6" s="2" t="n">
         <f aca="false">J6-K6</f>
-        <v>26000</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <f aca="false">ROUND(L6/J6*100,1)</f>
-        <v>19.3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="e">
+        <f aca="false">ROUND(L6/J6*100,1)=ROUND(L9/J9*100,1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
+        <f aca="false">SUM(B2:B6)</f>
         <v>560000</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
+        <f aca="false">SUM(C2:C6)</f>
         <v>390000</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
+        <f aca="false">SUM(D2:D6)</f>
         <v>617000</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
+        <f aca="false">SUM(E2:E6)</f>
         <v>416000</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
+        <f aca="false">SUM(F2:F6)</f>
         <v>680000</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
+        <f aca="false">SUM(G2:G6)</f>
         <v>443000</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
+        <f aca="false">SUM(H2:H6)</f>
         <v>758000</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="2" t="n">
+        <f aca="false">SUM(I2:I6)</f>
         <v>475000</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <f aca="false">SUM(J2:J6)</f>
-        <v>2615000</v>
-      </c>
-      <c r="K7" s="1" t="n">
+        <v>2694000</v>
+      </c>
+      <c r="K7" s="2" t="n">
         <f aca="false">SUM(K2:K6)</f>
-        <v>1724000</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <f aca="false">J7-K7</f>
-        <v>891000</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <f aca="false">ROUND(L7/J7*100,1)</f>
-        <v>34.1</v>
-      </c>
-    </row>
+        <v>1829000</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <f aca="false">SUM(L2:L6)</f>
+        <v>865000</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <f aca="false">L7/J7*100</f>
+        <v>32.1083890126206</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -547,11 +570,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -563,90 +586,181 @@
       <c r="D1" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!C3-'Q1-Q4'!B3)/'Q1-Q4'!B3*100,1)</f>
+        <v>-20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D3-'Q1-Q4'!C3)/'Q1-Q4'!C3*100,1)</f>
+        <v>37.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D3-'Q1-Q4'!E3)/'Q1-Q4'!E3*100,1)</f>
+        <v>32</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <f aca="false">B2*100</f>
+        <v>-2000</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <f aca="false">J2*0.7</f>
+        <v>-1400</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <f aca="false">J2-K2</f>
+        <v>-600</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <f aca="false">L2/J2*100</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!C4-'Q1-Q4'!B4)/'Q1-Q4'!B4*100,1)</f>
+        <v>-25</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D4-'Q1-Q4'!C4)/'Q1-Q4'!C4*100,1)</f>
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D4-'Q1-Q4'!E4)/'Q1-Q4'!E4*100,1)</f>
+        <v>38.5</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <f aca="false">B3*100</f>
+        <v>-2500</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <f aca="false">J3*0.7</f>
+        <v>-1750</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <f aca="false">J3-K3</f>
+        <v>-750</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <f aca="false">L3/J3*100</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="e">
+        <f aca="false">ROUND((#REF!-#REF!)/#REF!*100,1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C4" s="2" t="e">
+        <f aca="false">ROUND((#REF!-#REF!)/#REF!*100,1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D4" s="2" t="e">
+        <f aca="false">ROUND((#REF!-#REF!)/#REF!*100,1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J4" s="5" t="e">
+        <f aca="false">B4*100</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K4" s="5" t="e">
+        <f aca="false">J4*0.7</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L4" s="5" t="e">
+        <f aca="false">J4-K4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M4" s="5" t="e">
+        <f aca="false">L4/J4*100</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!C2-'Q1-Q4'!B2)/'Q1-Q4'!B2*100,1)</f>
+        <v>-50</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D2-'Q1-Q4'!C2)/'Q1-Q4'!C2*100,1)</f>
+        <v>120</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">ROUND(('Q1-Q4'!D2-'Q1-Q4'!E2)/'Q1-Q4'!E2*100,1)</f>
+        <v>100</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <f aca="false">B5*100</f>
+        <v>-5000</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <f aca="false">J5*0.7</f>
+        <v>-3500</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <f aca="false">J5-K5</f>
+        <v>-1500</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <f aca="false">L5/J5*100</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L6" s="5" t="e">
+        <f aca="false">SUM(L1:L5)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <f aca="false">IFERROR(L5/J5*100,0)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D2-'Q1-Q4'!B2)/'Q1-Q4'!B2*100,1)</f>
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!F2-'Q1-Q4'!D2)/'Q1-Q4'!D2*100,1)</f>
-        <v>13.6</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!H2-'Q1-Q4'!F2)/'Q1-Q4'!F2*100,1)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D3-'Q1-Q4'!B3)/'Q1-Q4'!B3*100,1)</f>
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!F3-'Q1-Q4'!D3)/'Q1-Q4'!D3*100,1)</f>
-        <v>9.1</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!H3-'Q1-Q4'!F3)/'Q1-Q4'!F3*100,1)</f>
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D4-'Q1-Q4'!B4)/'Q1-Q4'!B4*100,1)</f>
-        <v>12.5</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!F4-'Q1-Q4'!D4)/'Q1-Q4'!D4*100,1)</f>
-        <v>5.6</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!H4-'Q1-Q4'!F4)/'Q1-Q4'!F4*100,1)</f>
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D5-'Q1-Q4'!B5)/'Q1-Q4'!B5*100,1)</f>
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!F5-'Q1-Q4'!D5)/'Q1-Q4'!D5*100,1)</f>
-        <v>9.1</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!H5-'Q1-Q4'!F5)/'Q1-Q4'!F5*100,1)</f>
-        <v>8.3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!D6-'Q1-Q4'!B6)/'Q1-Q4'!B6*100,1)</f>
-        <v>6.7</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!F6-'Q1-Q4'!D6)/'Q1-Q4'!D6*100,1)</f>
-        <v>9.4</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <f aca="false">ROUND(('Q1-Q4'!H6-'Q1-Q4'!F6)/'Q1-Q4'!F6*100,1)</f>
-        <v>8.6</v>
+      <c r="B7" s="2" t="e">
+        <f aca="false">ROUND((#REF!-#REF!)/#REF!*100,1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C7" s="2" t="e">
+        <f aca="false">ROUND((#REF!-#REF!)/#REF!*100,1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D7" s="2" t="e">
+        <f aca="false">ROUND((#REF!-#REF!)/#REF!*100,1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J7" s="5" t="e">
+        <f aca="false">B7*100</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K7" s="5" t="e">
+        <f aca="false">SUM(K3:K7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
